--- a/input/Requirement Collection Sheet.xlsx
+++ b/input/Requirement Collection Sheet.xlsx
@@ -1,26 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankitbha\Desktop\ciq_automation\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4A02AF-81FC-4B43-A21D-D5D5AF728996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E94732-AF9D-4CEB-B5C9-1F8C275B2D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -42,14 +38,15 @@
     <author>Alexey 1. Smirnov (Nokia)</author>
   </authors>
   <commentList>
-    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{03B5EE49-6A4A-460D-9F53-DD7F1A4DF6FF}">
+    <comment ref="A25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
+            <scheme val="minor"/>
           </rPr>
           <t>Existing Mngt network does not have enough capacity to accommodate new HW</t>
         </r>
@@ -60,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="74">
   <si>
     <t>Name of parameter:</t>
   </si>
@@ -80,9 +77,15 @@
     <t>System name</t>
   </si>
   <si>
+    <t>ciqph</t>
+  </si>
+  <si>
     <t>Netact Target ID:</t>
   </si>
   <si>
+    <t>Nokia generated(example random value)</t>
+  </si>
+  <si>
     <t>Alphabet Start:</t>
   </si>
   <si>
@@ -98,9 +101,15 @@
     <t>Customer</t>
   </si>
   <si>
+    <t>CIQ Auto Proj</t>
+  </si>
+  <si>
     <t>CustomerID</t>
   </si>
   <si>
+    <t>Example random value</t>
+  </si>
+  <si>
     <t>CLS Target ID</t>
   </si>
   <si>
@@ -111,7 +120,9 @@
   </si>
   <si>
     <t>NetAct Domain Name:</t>
-    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>ciq.proj.automation</t>
   </si>
   <si>
     <t>LDAP BaseDN:</t>
@@ -120,100 +131,100 @@
     <t>Windows Domain:</t>
   </si>
   <si>
+    <t>ciqph1</t>
+  </si>
+  <si>
     <t>Prefix for VMs</t>
   </si>
   <si>
-    <t>CIQ Auto Proj</t>
-  </si>
-  <si>
-    <t>Example random value</t>
-  </si>
-  <si>
-    <t>ciq.proj.automation</t>
-  </si>
-  <si>
-    <t>ciqph1</t>
-  </si>
-  <si>
-    <t>Nokia generated(example random value)</t>
+    <t>nsn</t>
+  </si>
+  <si>
+    <t>Host_count</t>
+  </si>
+  <si>
+    <t>Below IP parameters are example values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VM_Network_SB </t>
+  </si>
+  <si>
+    <t>vlan 1000</t>
+  </si>
+  <si>
+    <t>Admin Server,  vCenter, NetAct VM, VDP etc.</t>
+  </si>
+  <si>
+    <t>VM_Network_SB subnet</t>
+  </si>
+  <si>
+    <t>172.24.59.0/26</t>
+  </si>
+  <si>
+    <t>network /26 with 62 hosts is sufficient</t>
+  </si>
+  <si>
+    <t>MASK:</t>
+  </si>
+  <si>
+    <t>255.255.255.192</t>
+  </si>
+  <si>
+    <t>42 ips used, it is needed to reserve 50 for future expansion</t>
+  </si>
+  <si>
+    <t>GW:</t>
+  </si>
+  <si>
+    <t>172.24.59.1</t>
+  </si>
+  <si>
+    <t>Range:</t>
+  </si>
+  <si>
+    <t>172.24.59.1 - 172.24.59.62</t>
+  </si>
+  <si>
+    <t>Hosts:</t>
+  </si>
+  <si>
+    <t>Management Network</t>
+  </si>
+  <si>
+    <t>vlan 1001</t>
+  </si>
+  <si>
+    <t>Old HP HW. ESXi hosts, OA, iLO, Storage, LAN switch etc.</t>
   </si>
   <si>
     <t>Management subnet</t>
   </si>
   <si>
-    <t>MASK:</t>
-  </si>
-  <si>
-    <t>GW:</t>
-  </si>
-  <si>
-    <t>Range:</t>
-  </si>
-  <si>
-    <t>Hosts:</t>
+    <t>172.24.59.64/27</t>
+  </si>
+  <si>
+    <t>network /27 with 32 hosts is sufficient</t>
+  </si>
+  <si>
+    <t>255.255.255.224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 Ips used, need to reserve 24. </t>
+  </si>
+  <si>
+    <t>172.24.59.65</t>
+  </si>
+  <si>
+    <t>172.24.59.65 - 172.24.59.94</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>Management Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VM_Network_SB </t>
-  </si>
-  <si>
-    <t>Admin Server,  vCenter, NetAct VM, VDP etc.</t>
-  </si>
-  <si>
-    <t>VM_Network_SB subnet</t>
-  </si>
-  <si>
-    <t>172.24.59.0/26</t>
-  </si>
-  <si>
-    <t>network /26 with 62 hosts is sufficient</t>
-  </si>
-  <si>
-    <t>255.255.255.192</t>
-  </si>
-  <si>
-    <t>42 ips used, it is needed to reserve 50 for future expansion</t>
-  </si>
-  <si>
-    <t>172.24.59.1</t>
-  </si>
-  <si>
-    <t>172.24.59.1 - 172.24.59.62</t>
-  </si>
-  <si>
-    <t>Old HP HW. ESXi hosts, OA, iLO, Storage, LAN switch etc.</t>
-  </si>
-  <si>
-    <t>172.24.59.64/27</t>
-  </si>
-  <si>
-    <t>network /27 with 32 hosts is sufficient</t>
-  </si>
-  <si>
-    <t>255.255.255.224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 Ips used, need to reserve 24. </t>
-  </si>
-  <si>
-    <t>172.24.59.65</t>
-  </si>
-  <si>
-    <t>172.24.59.65 - 172.24.59.94</t>
-  </si>
-  <si>
-    <t>vlan 1000</t>
-  </si>
-  <si>
-    <t>vlan 1001</t>
-  </si>
-  <si>
-    <t>Below IP parameters are example values</t>
+    <t xml:space="preserve">vMotion </t>
+  </si>
+  <si>
+    <t>vlan 1002</t>
   </si>
   <si>
     <t>not externally routed, only for vMotion purposes</t>
@@ -225,6 +236,9 @@
     <t>172.24.0.0/28</t>
   </si>
   <si>
+    <t xml:space="preserve">ips needed  based on physical  hosts present in system </t>
+  </si>
+  <si>
     <t>255.255.255.240</t>
   </si>
   <si>
@@ -234,27 +248,18 @@
     <t>14</t>
   </si>
   <si>
-    <t>vlan 1002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ips needed  based on physical  hosts present in system </t>
-  </si>
-  <si>
-    <t xml:space="preserve">vMotion </t>
-  </si>
-  <si>
-    <t>ciqph</t>
-  </si>
-  <si>
-    <t>Host_count</t>
-  </si>
-  <si>
     <t>OPTIONAL NODE</t>
   </si>
   <si>
     <t>RELEASE</t>
   </si>
   <si>
+    <t>Variant</t>
+  </si>
+  <si>
+    <t>Openstack , Vmware , BareMetal</t>
+  </si>
+  <si>
     <t>SWITCH DETAILS</t>
   </si>
   <si>
@@ -267,19 +272,13 @@
     <t>VIRTUAL CONNECT DETAILS</t>
   </si>
   <si>
-    <t>Variant</t>
-  </si>
-  <si>
-    <t>CLS,TP,SLC,LTE-A,LCM,CCR,NIV</t>
-  </si>
-  <si>
-    <t>Archit</t>
-  </si>
-  <si>
-    <t>OpenStack</t>
-  </si>
-  <si>
-    <t>MainStream</t>
+    <t>3xl</t>
+  </si>
+  <si>
+    <t>vmware</t>
+  </si>
+  <si>
+    <t>CLS,T&amp;P,SLC,NIV,JSON</t>
   </si>
 </sst>
 </file>
@@ -289,7 +288,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d&quot;-&quot;mmm;@"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -379,12 +378,6 @@
       <name val="Arial Unicode MS"/>
       <family val="3"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -487,10 +480,10 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="%" xfId="1" xr:uid="{B71F8F03-686B-4DA0-BB36-43F5C7230CBF}"/>
+    <cellStyle name="%" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal_IP and CLUSTER INFO 2" xfId="3" xr:uid="{04A976EC-9861-4284-8C24-B5DC1803A234}"/>
-    <cellStyle name="Normal_Sheet4 2" xfId="2" xr:uid="{4C7BEC46-7F00-4125-A509-9930E2B45D17}"/>
+    <cellStyle name="Normal_IP and CLUSTER INFO 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal_Sheet4 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -772,14 +765,14 @@
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="28.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.08984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.81640625" customWidth="1"/>
     <col min="5" max="5" width="19.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20">
+    <row r="1" spans="1:3" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -795,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -806,118 +799,118 @@
         <v>5</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" s="8">
         <v>20262601</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="9"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" s="9"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" s="8">
         <v>202626</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="11"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="7" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="26" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="B15" s="24">
         <v>0</v>
@@ -926,45 +919,45 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="26" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>34</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B20" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>37</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="17" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B21" s="23" t="s">
         <v>39</v>
@@ -973,16 +966,16 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="17" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="11"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="17" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B23" s="24">
         <v>62</v>
@@ -996,165 +989,159 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="14" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C28" s="16"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C29" s="16"/>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="17" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C30" s="16"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="17" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C35" s="9"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="17" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C36" s="22"/>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="17" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="17" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="17" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F39D25-F03E-4A5D-896F-C49420785AAE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>